--- a/Critical_Part_Type_Register.xlsx
+++ b/Critical_Part_Type_Register.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sources" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Register!$A$2:$N$31</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Register!$A$2:$Q$31</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Sources!$A$4:$D$46</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="610">
   <si>
     <t xml:space="preserve">Critical and Safety Critical Part Type Register</t>
   </si>
@@ -99,6 +99,39 @@
     <t xml:space="preserve">Rows flagged Verify</t>
   </si>
   <si>
+    <t xml:space="preserve">CI criterion (b) fit — direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI criterion (b) fit — conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI criterion (b) fit — no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI screening columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three columns on the Register map each designation onto the Configuration Item selection criteria, so a CI selection assessment can cite the right basis instead of treating every critical-part label as equivalent. Criterion (b) is the safety criterion: an item is designated a CI where its failure might cause serious injury, loss of life, or loss of primary system capability.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI criterion (b) fit. Direct means the designation attaches to an item satisfying a system end-use function and its stated consequence meets (b) on its own terms. Conditional means it fits only once translated onto an item, or only where the underlying limitation attaches to a discrete part. No means the designation does not reach the screen, almost always because the object designated is a feature, a task, a function, a failure mode or a location rather than an item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other CI criteria engaged. Criterion (b) is rarely the only one triggered. A government-assigned designation also engages (d); anything carrying provisioning, technical manual or dedicated test equipment obligations engages (g); an item the system cannot function without engages (a). Listing every criterion that applies matters, because the designation survives if one underlying fact later changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two cautions before using these columns as a screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Criterion (b) is wider than every row in this register on the loss of primary system capability limb. Nothing catalogued here keys on mission capability absent an injury pathway, so the register will under-catch. Treat it as an input to candidate identification, never as a substitute for the criteria screen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. A No in the criterion (b) column is not a finding that the item is uncontrolled, and not always a finding that it is not a CI. Items that are not CIs are controlled within their parent CI's configuration documentation, and several rows marked No still designate on criterion (a) — C11 most consequentially. Read the two columns together.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where a designation lands on an item, that item is safety-critical under the safety management system: a decision not to designate it a CI requires System Safety concurrence on the rationale and is dispositioned through the CM floor gate. It is not a CM call made alone, and it is never silently dropped.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Register of critical and safety critical part designations</t>
   </si>
   <si>
@@ -144,6 +177,15 @@
     <t xml:space="preserve">Confidence</t>
   </si>
   <si>
+    <t xml:space="preserve">CI criterion (b) fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other CI criteria engaged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI screening notes</t>
+  </si>
+  <si>
     <t xml:space="preserve">C01</t>
   </si>
   <si>
@@ -186,6 +228,15 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(d), (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statutory definition maps onto criterion (b) almost word for word: catastrophic or critical failure, loss of life, unacceptable risk of injury. Assigned by the government engineering activity, so criterion (d) engages as well and CM records the designation rather than determining it. Spares and sustainment reach brings logistics elements, engaging (g).</t>
+  </si>
+  <si>
     <t xml:space="preserve">C02</t>
   </si>
   <si>
@@ -216,6 +267,9 @@
     <t xml:space="preserve">Verify</t>
   </si>
   <si>
+    <t xml:space="preserve">Same statutory construct, same screen. Level I and SUBSAFE objective quality evidence is a control on the item, not a substitute for designation. Where the item is not separately designated, control sits in the parent CI's documentation and that rationale needs recording.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C03</t>
   </si>
   <si>
@@ -246,6 +300,12 @@
     <t xml:space="preserve">Related legacy variants include Flight Safety Part and Flight Safety Critical Part. If a legacy drawing carries one of these, map it to the current CSI construct rather than assuming equivalence.</t>
   </si>
   <si>
+    <t xml:space="preserve">(d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy label. Screens (b) on its own wording, but map it to the current CSI construct before relying on it rather than assuming equivalence. A legacy drawing note carrying this term is a candidate-identification input, not a designation record.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C04</t>
   </si>
   <si>
@@ -282,6 +342,12 @@
     <t xml:space="preserve">This is a catalogue flag rather than an engineering designation. Confirm current criticality code definitions in FLIS before citing specific code letters.</t>
   </si>
   <si>
+    <t xml:space="preserve">None on its own</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A catalogue flag applied to a stock number, not an engineering determination. Fails the end-use function gate as written because the object is a supply code. Follow the flag back to the underlying engineering designation and screen that item; the coding itself never designates a CI.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C05</t>
   </si>
   <si>
@@ -315,6 +381,12 @@
     <t xml:space="preserve">Obligation is the three plan structure: Engineering Plan, Manufacturing Plan, Service Management Plan. Appears in the engine manual because the ALS lives there, but the designation is made at type certification.</t>
   </si>
   <si>
+    <t xml:space="preserve">(a), (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazardous engine effect reaches (b) through both the serious-injury and the loss-of-primary-system-capability limbs. The three-plan integrity structure is configuration documentation and belongs to the CI's baseline; the Engineering Plan in particular is what makes influencing parts visible (see C11).</t>
+  </si>
+  <si>
     <t xml:space="preserve">C06</t>
   </si>
   <si>
@@ -345,6 +417,9 @@
     <t xml:space="preserve">The clearest case in the whole register. Remaining life is a per unit quantity, so the unit must be individually identifiable. Cycle counting drives serialization directly.</t>
   </si>
   <si>
+    <t xml:space="preserve">The clearest case in the register. Remaining life is a per-unit quantity, so the unit identifier must persist across PIN changes and back-to-birth records are status accounting against the CI. Logistics elements are unavoidable, engaging (g).</t>
+  </si>
+  <si>
     <t xml:space="preserve">C07</t>
   </si>
   <si>
@@ -372,6 +447,9 @@
     <t xml:space="preserve">Same three plan integrity structure as CS-E 515. The Engineering Plan wording explicitly requires accounting for the effects of parts influencing the load, material, environmental, and operating condition parameters, which is the origin of the influencing part concept.</t>
   </si>
   <si>
+    <t xml:space="preserve">Constructed identically to the engine critical part. Hazardous propeller effect engages (b) directly; the same three-plan documentation structure applies and forms part of the CI's configuration documentation.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C08</t>
   </si>
   <si>
@@ -396,6 +474,12 @@
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
+    <t xml:space="preserve">(g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaches (b) through the serious-injury limb rather than loss of primary system capability, since an APU is rarely primary capability. Weakest of the three hazardous-effect constructs on consequence, but the screen is met and the designation follows.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C09</t>
   </si>
   <si>
@@ -426,6 +510,9 @@
     <t xml:space="preserve">Note the structural difference from the engine definition: this one is expressed in terms of critical characteristics that must be controlled, which pushes the obligation down to the feature level as well as the part level.</t>
   </si>
   <si>
+    <t xml:space="preserve">Catastrophic effect on the rotorcraft engages (b) squarely. Note the definition pushes control down to identified critical characteristics: the part is the CI, the characteristics are controlled within its documentation. Do not designate characteristics as CIs to make records match.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C10</t>
   </si>
   <si>
@@ -453,6 +540,9 @@
     <t xml:space="preserve">Useful because it is the definition most likely to appear in an export or transfer agreement rather than in a certification basis. Do not import it into a design context.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hits by inheritance rather than by independent determination: the defining population is the set of parts already carrying ALS or CMR provisions. Screen the underlying limitation, not the export label. Do not import this definition into a design context, where it will over-designate.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C11</t>
   </si>
   <si>
@@ -489,6 +579,15 @@
     <t xml:space="preserve">Highest exposure row in the register. The airworthiness consequence is displaced onto a different part number, so a critical part can remain within its stamped life limit while the lifing basis underneath it has quietly become invalid. Typical examples are cooling air metering hardware, seals, bearings, and oil nozzles.</t>
   </si>
   <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a), (f)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The trap in this register. Fails (b) by its own definition, since its own failure has no hazardous effect, yet it is a strong candidate on (a): the approved lifing basis of a safety-critical part depends on its configuration, and a change to it needs an independent effectivity address. Screening only against (b) and stopping is exactly how a CIP goes undesignated while a critical part sits within its stamped life on an invalid basis.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C12</t>
   </si>
   <si>
@@ -522,6 +621,9 @@
     <t xml:space="preserve">The ALS is the practical trigger mechanism for most civil serialization. Work from the ALS content rather than from the criticality label when determining marking obligations.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fits where the limitation attaches to a discrete part. A zonal or structural inspection task has no item to designate and is controlled within the parent CI's documentation. Work from what is actually in the ALS rather than from the criticality label, per the workbook's own recording rule.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C13</t>
   </si>
   <si>
@@ -555,6 +657,9 @@
     <t xml:space="preserve">Included because CMRs sit adjacent to ALIs in the same document and are frequently conflated with them. They have different origins and different change control paths.</t>
   </si>
   <si>
+    <t xml:space="preserve">A task, not an item, so it never reaches the criteria screen. Its existence is still a candidate-identification signal: a CMR means the certification safety analysis found a latent failure contributing to a hazardous or catastrophic condition, so screen the items implementing that function against (b).</t>
+  </si>
+  <si>
     <t xml:space="preserve">C14</t>
   </si>
   <si>
@@ -588,6 +693,9 @@
     <t xml:space="preserve">Related terms in the same family include Fatigue Critical Structure and Fatigue Critical Baseline Structure. All are location based rather than part based, which is why they generate no marking obligation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Location-based, tracked by tail number and structural location rather than by part identity, so it fails the object test. The underlying detail parts may be CI candidates on their own merits. Fatigue Critical Structure and Fatigue Critical Baseline Structure behave identically.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C15</t>
   </si>
   <si>
@@ -624,6 +732,12 @@
     <t xml:space="preserve">Scoped by failure mechanism rather than by consequence generally. Asks what happens if this part cracks, not what happens if it fails, and exists to trigger fracture mechanics obligations rather than source control.</t>
   </si>
   <si>
+    <t xml:space="preserve">(a), (c)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrying flight, ground or pressurization loads is an end-use function, so this clears the gate that purely structural elements with no functional role fail. Scoped by failure mechanism rather than consequence generally, but the consequence stated -- loss of the aircraft -- meets (b). Fracture control records belong to the product baseline.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C16</t>
   </si>
   <si>
@@ -651,6 +765,9 @@
     <t xml:space="preserve">The precision matters. Within ASIP it is the traceable subclass that carries the serialization obligation, not fracture critical status in general. A compliance matrix that cites fracture critical alone will not support the marking requirement.</t>
   </si>
   <si>
+    <t xml:space="preserve">Same screen as C15, with the serialization obligation attaching to this subclass specifically. When the marking requirement is what matters, cite this class rather than fracture critical generally -- the distinction survives into the CI index and the traceability record.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C17</t>
   </si>
   <si>
@@ -684,6 +801,12 @@
     <t xml:space="preserve">Because MIL-STD-1783 was cancelled and only the handbook survives, fracture critical status on a modern engine contract usually rests on program specific SOW language rather than on a citable standard. Check the contract, not the handbook.</t>
   </si>
   <si>
+    <t xml:space="preserve">(a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consequence meets (b) regardless of the citation problem. Because the standard was cancelled and only the handbook survives, the designation usually rests on program SOW language: screen the item on consequence and record the contractual basis in the selection rationale so the next assessor can see where it came from.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C18</t>
   </si>
   <si>
@@ -717,6 +840,9 @@
     <t xml:space="preserve">Obligation set is assumed initial flaw size, damage tolerance or safe life analysis, NDE with demonstrated probability of detection, controlled processing, and derived inspection intervals.</t>
   </si>
   <si>
+    <t xml:space="preserve">Catastrophic hazard by definition, so (b) is met. The fracture control record set -- assumed initial flaw size, damage tolerance or safe life analysis, NDE with demonstrated probability of detection, derived inspection intervals -- is per part and forms part of the CI's product configuration information.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C19</t>
   </si>
   <si>
@@ -747,6 +873,9 @@
     <t xml:space="preserve">Same logic as the aerospace usage: a nonredundant tension member whose single crack driven failure removes the load path. Confirm the current terminology and citation, since the fracture critical to NSTM transition postdates much of the existing literature.</t>
   </si>
   <si>
+    <t xml:space="preserve">Outside the manufactured-product domain: identity is a member in a bridge inventory, not a part number, and there is no system end-use function in the CI sense. Present in the register for terminology contrast only; it should not appear in a CI screening decision.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C20</t>
   </si>
   <si>
@@ -783,6 +912,9 @@
     <t xml:space="preserve">Distinctive for encoding redundancy in the code itself, unlike the DoD CSI construct where system level redundancy does not relieve the designation. The obligation is documented retention rationale plus program acceptance rather than a hardware control.</t>
   </si>
   <si>
+    <t xml:space="preserve">The object is a failure mode, not an item, so the code alone designates nothing. Translate it to the hardware implementing that mode and screen that hardware against (b). Note that 1R carries the same consequence as 1 -- redundancy does not relieve the screen, matching the CI criteria, which contain no likelihood or redundancy term.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C21</t>
   </si>
   <si>
@@ -819,6 +951,9 @@
     <t xml:space="preserve">Scoped by accident analysis rather than by part failure effect, which is the structural difference from CSI. Adjacent categories include important to safety and augmented quality, which carry reduced obligations.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fits at component level, where failure defeats safe shutdown or containment. System-level SSC scoping sits above CI level and decomposes into CIs. Worth noting that commercial grade dedication accepts a catastrophic-consequence item on a lot basis -- a legitimate (b) item that is not serialized.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C22</t>
   </si>
   <si>
@@ -852,6 +987,12 @@
     <t xml:space="preserve">Frequently confused with the DFARS critical safety item. Different authority, different object, different obligation. MIL-STD-882E also drives the software criticality index and level of rigor tasks, which are process obligations rather than part obligations.</t>
   </si>
   <si>
+    <t xml:space="preserve">(a), SW rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The safety-critical ITEM half is the direct hit and is the designation the safety-linkage rule is written for: screen against (b), and usually (a). The safety-critical FUNCTION half designates a function and produces no CI candidate on its own. Software items go to CSCI by rule, not by judgement.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C23</t>
   </si>
   <si>
@@ -885,6 +1026,12 @@
     <t xml:space="preserve">Aimed at development error rather than part conformance, which is why a Level A function can be implemented with parts that are not critical parts. Assignment is top down and can be reduced by architecture and independence, unlike CSI.</t>
   </si>
   <si>
+    <t xml:space="preserve">SW rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designates development rigor for a function or a baseline, not consequence for an item. A Level A function can be implemented with parts that are not (b) items, and the reverse also holds. What gets uniquely identified is the loadable part number and baseline; the software is a CSCI by rule regardless of level.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C24</t>
   </si>
   <si>
@@ -921,6 +1068,9 @@
     <t xml:space="preserve">Risk based rather than consequence only, and reducible through decomposition. The contrast with CSI is sharp: exposure and controllability have no place in a CSI determination.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cannot proxy for (b). ASIL discounts by exposure and controllability; criterion (b) is consequence-only. A catastrophic-severity, low-exposure hazard scores a low ASIL and still meets (b) in full. Using an integrity level as the screen systematically under-designates exactly the low-exposure, high-consequence items.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C25</t>
   </si>
   <si>
@@ -951,6 +1101,9 @@
     <t xml:space="preserve">Quantitative target plus architectural constraint plus process rigor. Assigned to a function, not to an item, so it never attaches cleanly to a part number.</t>
   </si>
   <si>
+    <t xml:space="preserve">Assigned to a safety function with a quantitative target and architectural constraints; it never attaches cleanly to a part number. Same likelihood-discount objection as ASIL. Instrument tag identity in an asset register is not a CI identifier.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C26</t>
   </si>
   <si>
@@ -981,6 +1134,9 @@
     <t xml:space="preserve">Included to show that the process rigor pattern recurs identically outside aerospace under a different label.</t>
   </si>
   <si>
+    <t xml:space="preserve">Largely moot for designation: software is designated a CSCI by rule, so the class changes nothing about whether it is a CI. Class C is still useful evidence -- it signals the hazard severity that would engage (b) for the hosting hardware item and for anything else in that hazard path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C27</t>
   </si>
   <si>
@@ -1017,6 +1173,12 @@
     <t xml:space="preserve">Note that the AS9100 term critical item is deliberately broader than safety and includes producibility, service life, form, fit and function. Do not treat an AS9100 critical item as equivalent to a safety critical designation without checking why it was flagged.</t>
   </si>
   <si>
+    <t xml:space="preserve">(a) for the parent part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attaches to a feature or process parameter, not an item, and is controlled within the parent CI's documentation. Strong evidence the parent part is a (b) candidate -- screen the part, not the characteristic. Note the AS9100 'critical item' term is deliberately broader than safety and includes producibility, service life and form/fit/function; check why it was flagged before treating it as safety-critical.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C28</t>
   </si>
   <si>
@@ -1053,6 +1215,9 @@
     <t xml:space="preserve">Performance based rather than list based. Each element carries a written performance standard, and an independent verification scheme confirms suitability and continued performance. No source approval concept at all, which is the opposite pole from CSI.</t>
   </si>
   <si>
+    <t xml:space="preserve">Element-level and performance-standard based, identified by asset tag rather than part number. Fits where the element is a manufactured item satisfying an end-use function. The written scheme of verification is an independent assurance mechanism, not a configuration designation, and does not substitute for one.</t>
+  </si>
+  <si>
     <t xml:space="preserve">C29</t>
   </si>
   <si>
@@ -1084,6 +1249,12 @@
   </si>
   <si>
     <t xml:space="preserve">The only regime in this register where the risk classification itself, rather than a life limit or an inspection history, drives unique marking. Useful as a contrast case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(e), (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk classification drives the marking, not a consequence screen of the item's failure, so it does not itself satisfy (b). In practice the device is the end item and therefore the top-level CI in its own right. Useful contrast case: the only regime here where the classification itself compels unique marking.</t>
   </si>
   <si>
     <t xml:space="preserve">Cross-cutting record keeping drivers</t>
@@ -1861,16 +2032,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1890,7 +2065,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1914,6 +2089,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1926,6 +2105,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1934,15 +2121,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2275,175 +2458,239 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="118"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="118"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="7" t="n">
         <f aca="false">COUNTA(Register!B3:B60)</f>
         <v>29</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="7" t="n">
         <f aca="false">COUNTIF(Register!J3:J60,"Required")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="7" t="n">
         <f aca="false">COUNTIF(Register!J3:J60,"Conditional")</f>
         <v>9</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="7" t="n">
         <f aca="false">COUNTIF(Register!J3:J60,"Not required")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="7" t="n">
         <f aca="false">COUNTIF(Register!J3:J60,"Not applicable")</f>
         <v>7</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="7" t="n">
         <f aca="false">COUNTIF(Register!N3:N60,"Verify")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <f aca="false">COUNTIF(Register!O3:O60,"Direct")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <f aca="false">COUNTIF(Register!O3:O60,"Conditional")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="7" t="n">
+        <f aca="false">COUNTIF(Register!O3:O60,"No")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2461,1365 +2708,1638 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>37</v>
       </c>
+      <c r="D2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>51</v>
+      <c r="A3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="13" t="s">
+      <c r="A4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="13" t="s">
+      <c r="E4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="N4" s="15" t="s">
+      <c r="H4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>61</v>
       </c>
+      <c r="K4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4" s="15" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="A5" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q5" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="N7" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="O7" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="P7" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="O10" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="P12" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="N5" s="16" t="s">
+      <c r="Q12" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="K14" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="J16" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="N16" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O16" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="N20" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O20" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="N21" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="N6" s="15" t="s">
+      <c r="O21" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="P21" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="I22" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="J22" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="N22" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="O22" s="18" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="M8" s="13" t="s">
+      <c r="P22" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q22" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="J23" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O23" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="P23" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q23" s="10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="J24" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="N24" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q24" s="15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q25" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="N26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="P26" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="N8" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="Q26" s="15" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="P27" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q27" s="10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="N28" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="O28" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="P28" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q28" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="J29" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="N29" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="O29" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q29" s="10" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="N30" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="O30" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="P30" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="M10" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="N10" s="18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="10" t="s">
+      <c r="Q30" s="15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="L12" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="N12" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="H31" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="N31" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="N15" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="N16" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="N17" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="N18" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="N20" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="N21" s="16" t="s">
+      <c r="O31" s="13" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="N22" s="18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="M24" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="N24" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>295</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="M28" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="N28" s="18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="J30" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="N30" s="18" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="108" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="J31" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>121</v>
+      <c r="P31" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="Q31" s="10" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N31"/>
+  <autoFilter ref="A2:Q31"/>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3842,195 +4362,195 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>36</v>
+      <c r="A4" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>362</v>
+      <c r="A5" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>366</v>
+      <c r="A6" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>370</v>
+      <c r="A7" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>371</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>375</v>
+      <c r="A8" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>380</v>
+      <c r="A9" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>384</v>
+      <c r="A10" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>388</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>389</v>
+      <c r="A11" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>394</v>
+      <c r="A12" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>399</v>
+      <c r="A13" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -4055,148 +4575,148 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>401</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>405</v>
+      <c r="A4" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>408</v>
+      <c r="A5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>409</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>412</v>
+      <c r="A6" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>416</v>
+      <c r="A7" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>420</v>
+      <c r="A8" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>424</v>
+      <c r="A9" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>427</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>428</v>
+      <c r="A10" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>432</v>
+      <c r="A11" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>436</v>
+      <c r="A12" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4221,625 +4741,625 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>442</v>
+      <c r="A4" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>38</v>
+      <c r="A5" s="11" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>449</v>
+      <c r="A6" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>38</v>
+      <c r="A7" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>527</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>552</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>584</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>590</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>594</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="11" t="s">
+        <v>599</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>454</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>456</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>458</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>464</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>468</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>460</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>473</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>479</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="s">
-        <v>482</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>484</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>477</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="s">
-        <v>487</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>494</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>498</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>500</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>504</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>509</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>510</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>512</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>516</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>522</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>519</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
-        <v>523</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>524</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>527</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="s">
-        <v>532</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>528</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>536</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="s">
-        <v>540</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10" t="s">
-        <v>542</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>544</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>545</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>546</v>
+      <c r="B44" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>229</v>
+      <c r="A45" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>605</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="s">
-        <v>550</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>551</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>552</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>329</v>
+      <c r="A46" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>
